--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.95122199330353</v>
+        <v>5.842073573911823</v>
       </c>
       <c r="D2" t="n">
-        <v>35.95122199330353</v>
+        <v>5.842073573911823</v>
       </c>
       <c r="E2" t="n">
-        <v>9.786954142830908</v>
+        <v>1.590380048210022</v>
       </c>
       <c r="F2" t="n">
-        <v>5.889791447367247</v>
+        <v>0.9570911101971775</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.37757025658961</v>
+        <v>8.023855166695812</v>
       </c>
       <c r="D3" t="n">
-        <v>28.79518885289556</v>
+        <v>4.679218188595528</v>
       </c>
       <c r="E3" t="n">
-        <v>9.786954142830908</v>
+        <v>1.590380048210022</v>
       </c>
       <c r="F3" t="n">
-        <v>5.889791447367247</v>
+        <v>0.9570911101971775</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.46468681033448</v>
+        <v>4.138011606679354</v>
       </c>
       <c r="D4" t="n">
-        <v>21.52439041450534</v>
+        <v>3.497713442357118</v>
       </c>
       <c r="E4" t="n">
-        <v>9.786954142830908</v>
+        <v>1.590380048210022</v>
       </c>
       <c r="F4" t="n">
-        <v>5.889791447367247</v>
+        <v>0.9570911101971775</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
